--- a/outputs/analysis/attribution_models.xlsx
+++ b/outputs/analysis/attribution_models.xlsx
@@ -52,12 +52,12 @@
     <t>6sense_event</t>
   </si>
   <si>
+    <t>6sense_display</t>
+  </si>
+  <si>
     <t>email_mqa</t>
   </si>
   <si>
-    <t>6sense_display</t>
-  </si>
-  <si>
     <t>webinar</t>
   </si>
   <si>
@@ -70,7 +70,7 @@
     <t>$1,535,086</t>
   </si>
   <si>
-    <t>$1,100,230</t>
+    <t>$1,090,230</t>
   </si>
   <si>
     <t>$677,725</t>
@@ -79,12 +79,12 @@
     <t>$624,991</t>
   </si>
   <si>
-    <t>$91,226</t>
-  </si>
-  <si>
     <t>$89,016</t>
   </si>
   <si>
+    <t>$57,033</t>
+  </si>
+  <si>
     <t>$39,232</t>
   </si>
   <si>
@@ -115,43 +115,43 @@
     <t>Marketing Sourced</t>
   </si>
   <si>
-    <t>$3,625,867</t>
-  </si>
-  <si>
-    <t>$2,716,112</t>
+    <t>$3,610,867</t>
+  </si>
+  <si>
+    <t>$2,745,194</t>
   </si>
   <si>
     <t>$562,646</t>
   </si>
   <si>
-    <t>$224,743</t>
+    <t>$263,825</t>
   </si>
   <si>
     <t>Marketing Influenced</t>
   </si>
   <si>
-    <t>$4,055,120</t>
-  </si>
-  <si>
-    <t>$2,286,860</t>
+    <t>$4,035,120</t>
+  </si>
+  <si>
+    <t>$2,320,942</t>
   </si>
   <si>
     <t>$583,987</t>
   </si>
   <si>
-    <t>$203,401</t>
+    <t>$242,483</t>
   </si>
   <si>
     <t>First-Touch</t>
   </si>
   <si>
-    <t>$3,231,875</t>
-  </si>
-  <si>
-    <t>$3,110,104</t>
-  </si>
-  <si>
-    <t>$303,755</t>
+    <t>$3,255,957</t>
+  </si>
+  <si>
+    <t>$3,100,104</t>
+  </si>
+  <si>
+    <t>$342,837</t>
   </si>
   <si>
     <t>$483,634</t>
@@ -163,16 +163,16 @@
     <t>Linear</t>
   </si>
   <si>
-    <t>$3,312,179</t>
-  </si>
-  <si>
-    <t>$3,029,801</t>
-  </si>
-  <si>
-    <t>$285,822</t>
-  </si>
-  <si>
-    <t>$501,567</t>
+    <t>$3,341,530</t>
+  </si>
+  <si>
+    <t>$3,014,532</t>
+  </si>
+  <si>
+    <t>$327,495</t>
+  </si>
+  <si>
+    <t>$498,976</t>
   </si>
   <si>
     <t>Time-Decay</t>
@@ -610,7 +610,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -627,7 +627,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -644,7 +644,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -678,7 +678,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -695,7 +695,7 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
@@ -843,7 +843,7 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -884,10 +884,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -895,16 +895,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2">
-        <v>509</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
         <v>37</v>
+      </c>
+      <c r="D2">
+        <v>501</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
@@ -912,16 +912,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="C3">
-        <v>186</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s">
         <v>38</v>
+      </c>
+      <c r="D3">
+        <v>183</v>
       </c>
       <c r="E3" t="s">
         <v>39</v>
@@ -945,10 +945,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -956,16 +956,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>268</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
         <v>42</v>
+      </c>
+      <c r="D2">
+        <v>264</v>
       </c>
       <c r="E2" t="s">
         <v>44</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
       </c>
-      <c r="C3">
-        <v>427</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s">
         <v>43</v>
+      </c>
+      <c r="D3">
+        <v>420</v>
       </c>
       <c r="E3" t="s">
         <v>44</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
@@ -1026,7 +1026,7 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E2" t="s">
         <v>45</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -1043,7 +1043,7 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -1087,7 +1087,7 @@
         <v>48</v>
       </c>
       <c r="D2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E2" t="s">
         <v>50</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -1104,7 +1104,7 @@
         <v>49</v>
       </c>
       <c r="D3">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
@@ -1168,25 +1168,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>2286859.82</v>
+        <v>2320941.82</v>
       </c>
       <c r="C3">
-        <v>3231875.4</v>
+        <v>3255957.4</v>
       </c>
       <c r="D3">
-        <v>2716112.2</v>
+        <v>2745194.2</v>
       </c>
       <c r="E3">
-        <v>2716112.2</v>
+        <v>2745194.2</v>
       </c>
       <c r="F3">
         <v>89016</v>
       </c>
       <c r="G3">
-        <v>3312178.694695475</v>
+        <v>3341529.821121865</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1214,25 +1214,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>4055119.54</v>
+        <v>4035119.54</v>
       </c>
       <c r="C5">
-        <v>3110103.96</v>
+        <v>3100103.96</v>
       </c>
       <c r="D5">
-        <v>3625867.16</v>
+        <v>3610867.16</v>
       </c>
       <c r="E5">
-        <v>3625867.16</v>
+        <v>3610867.16</v>
       </c>
       <c r="F5">
-        <v>91226.5</v>
+        <v>57033</v>
       </c>
       <c r="G5">
-        <v>3029800.665304525</v>
+        <v>3014531.538878135</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1321,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1100230</v>
+        <v>1090230</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1406,34 +1406,34 @@
         <v>365</v>
       </c>
       <c r="B2">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C2">
-        <v>3166</v>
+        <v>3129</v>
       </c>
       <c r="D2">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="E2">
-        <v>0.211374695863747</v>
+        <v>0.2107858243451464</v>
       </c>
       <c r="F2">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I2">
-        <v>0.1174277726001864</v>
+        <v>0.1186915887850467</v>
       </c>
       <c r="J2">
-        <v>6341979.359999999</v>
+        <v>6356061.359999999</v>
       </c>
       <c r="K2">
-        <v>787388.5700000001</v>
+        <v>826470.5699999999</v>
       </c>
       <c r="L2" t="s">
         <v>64</v>
@@ -1498,34 +1498,34 @@
         <v>30</v>
       </c>
       <c r="B2">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C2">
-        <v>3166</v>
+        <v>3129</v>
       </c>
       <c r="D2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E2">
-        <v>0.1310827250608272</v>
+        <v>0.1303543913713405</v>
       </c>
       <c r="F2">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>0.06057781919850885</v>
+        <v>0.0616822429906542</v>
       </c>
       <c r="J2">
-        <v>3995089.25</v>
+        <v>4053980.25</v>
       </c>
       <c r="K2">
-        <v>553783</v>
+        <v>592865</v>
       </c>
       <c r="L2" t="s">
         <v>64</v>
@@ -1539,34 +1539,34 @@
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C3">
-        <v>3166</v>
+        <v>3129</v>
       </c>
       <c r="D3">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E3">
-        <v>0.180352798053528</v>
+        <v>0.1799691833590139</v>
       </c>
       <c r="F3">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G3">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I3">
-        <v>0.09412861136999068</v>
+        <v>0.09532710280373832</v>
       </c>
       <c r="J3">
-        <v>5674641.189999999</v>
+        <v>5688723.189999999</v>
       </c>
       <c r="K3">
-        <v>754341.3300000001</v>
+        <v>793423.3300000001</v>
       </c>
       <c r="L3" t="s">
         <v>64</v>
@@ -1580,34 +1580,34 @@
         <v>180</v>
       </c>
       <c r="B4">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C4">
-        <v>3166</v>
+        <v>3129</v>
       </c>
       <c r="D4">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="E4">
-        <v>0.2019464720194647</v>
+        <v>0.2015408320493066</v>
       </c>
       <c r="F4">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G4">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I4">
-        <v>0.1099720410065238</v>
+        <v>0.111214953271028</v>
       </c>
       <c r="J4">
-        <v>6199104.02</v>
+        <v>6213186.02</v>
       </c>
       <c r="K4">
-        <v>785815.23</v>
+        <v>824897.2299999999</v>
       </c>
       <c r="L4" t="s">
         <v>64</v>
@@ -1621,34 +1621,34 @@
         <v>365</v>
       </c>
       <c r="B5">
-        <v>3288</v>
+        <v>3245</v>
       </c>
       <c r="C5">
-        <v>3166</v>
+        <v>3129</v>
       </c>
       <c r="D5">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="E5">
-        <v>0.211374695863747</v>
+        <v>0.2107858243451464</v>
       </c>
       <c r="F5">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G5">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H5">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I5">
-        <v>0.1174277726001864</v>
+        <v>0.1186915887850467</v>
       </c>
       <c r="J5">
-        <v>6341979.359999999</v>
+        <v>6356061.359999999</v>
       </c>
       <c r="K5">
-        <v>787388.5700000001</v>
+        <v>826470.5699999999</v>
       </c>
       <c r="L5" t="s">
         <v>64</v>
